--- a/Res_ConvLSTM/DroughtDataset_model_testing_1751026745_individual_h_10.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1751026745_individual_h_10.xlsx
@@ -658,7 +658,7 @@
         <v>0.008508942972900661</v>
       </c>
       <c r="C2" t="n">
-        <v>63463800</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>63463800</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>44199772</v>
+        <v>4081352</v>
       </c>
       <c r="L2" t="n">
-        <v>23473455</v>
+        <v>1695235</v>
       </c>
       <c r="M2" t="n">
-        <v>5595878</v>
+        <v>340197</v>
       </c>
       <c r="N2" t="n">
-        <v>269049</v>
+        <v>5468</v>
       </c>
       <c r="O2" t="n">
-        <v>3322977</v>
+        <v>180910</v>
       </c>
       <c r="P2" t="n">
-        <v>1263308</v>
+        <v>59385</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999533295631409</v>
+        <v>0.999873161315918</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8441430330276489</v>
+        <v>0.7303629517555237</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7219205498695374</v>
+        <v>0.5516936779022217</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6531668305397034</v>
+        <v>0.4183178544044495</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2904276847839355</v>
+        <v>0.04912362620234489</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6973945498466492</v>
+        <v>0.4642753601074219</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8103899359703064</v>
+        <v>0.6338118314743042</v>
       </c>
       <c r="X2" t="n">
-        <v>63463800</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>63463800</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>48303112</v>
+        <v>4789433</v>
       </c>
       <c r="AG2" t="n">
-        <v>29981680</v>
+        <v>3027015</v>
       </c>
       <c r="AH2" t="n">
-        <v>8027267</v>
+        <v>807060</v>
       </c>
       <c r="AI2" t="n">
-        <v>591860</v>
+        <v>59367</v>
       </c>
       <c r="AJ2" t="n">
-        <v>4598515</v>
+        <v>461241</v>
       </c>
       <c r="AK2" t="n">
-        <v>1801493</v>
+        <v>180417</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9560742974281311</v>
+        <v>0.9549785256385803</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.911531388759613</v>
+        <v>0.912082850933075</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8580335974693298</v>
+        <v>0.8579939603805542</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.661676824092865</v>
+        <v>0.6605360507965088</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9019646048545837</v>
+        <v>0.90191650390625</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314513206481934</v>
+        <v>0.9314922094345093</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002036865544291333</v>
       </c>
       <c r="C3" t="n">
-        <v>412</v>
+        <v>156</v>
       </c>
       <c r="D3" t="n">
-        <v>44199772</v>
+        <v>4081352</v>
       </c>
       <c r="E3" t="n">
-        <v>6040735</v>
+        <v>876290</v>
       </c>
       <c r="F3" t="n">
-        <v>175764</v>
+        <v>39413</v>
       </c>
       <c r="G3" t="n">
-        <v>15438</v>
+        <v>2504</v>
       </c>
       <c r="H3" t="n">
-        <v>12905</v>
+        <v>3113</v>
       </c>
       <c r="I3" t="n">
-        <v>837</v>
+        <v>162</v>
       </c>
       <c r="J3" t="n">
-        <v>100693239</v>
+        <v>10068815</v>
       </c>
       <c r="K3" t="n">
-        <v>105553385</v>
+        <v>9906247</v>
       </c>
       <c r="L3" t="n">
-        <v>122164846</v>
+        <v>11710067</v>
       </c>
       <c r="M3" t="n">
-        <v>151823100</v>
+        <v>15000423</v>
       </c>
       <c r="N3" t="n">
-        <v>162607312</v>
+        <v>16220179</v>
       </c>
       <c r="O3" t="n">
-        <v>157616551</v>
+        <v>15695311</v>
       </c>
       <c r="P3" t="n">
-        <v>161929806</v>
+        <v>16187885</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8761823177337646</v>
+        <v>0.8157825469970703</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7123244404792786</v>
+        <v>0.5093265771865845</v>
       </c>
       <c r="T3" t="n">
-        <v>0.597500741481781</v>
+        <v>0.360942542552948</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3004965782165527</v>
+        <v>0.06077041104435921</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6513621807098389</v>
+        <v>0.3533826470375061</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6530029773712158</v>
+        <v>0.306416243314743</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>48303112</v>
+        <v>4789433</v>
       </c>
       <c r="Z3" t="n">
-        <v>1988133</v>
+        <v>198166</v>
       </c>
       <c r="AA3" t="n">
-        <v>85525</v>
+        <v>8476</v>
       </c>
       <c r="AB3" t="n">
-        <v>68445</v>
+        <v>6874</v>
       </c>
       <c r="AC3" t="n">
-        <v>348</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>100696200</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>111494909</v>
+        <v>11187217</v>
       </c>
       <c r="AG3" t="n">
-        <v>128296811</v>
+        <v>12795836</v>
       </c>
       <c r="AH3" t="n">
-        <v>153466369</v>
+        <v>15339900</v>
       </c>
       <c r="AI3" t="n">
-        <v>162962027</v>
+        <v>16295512</v>
       </c>
       <c r="AJ3" t="n">
-        <v>158558602</v>
+        <v>15853902</v>
       </c>
       <c r="AK3" t="n">
-        <v>162092809</v>
+        <v>16208926</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575237631797791</v>
+        <v>0.957314133644104</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9098227620124817</v>
+        <v>0.9094545841217041</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8571126461029053</v>
+        <v>0.8562752604484558</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6610390543937683</v>
+        <v>0.6597946286201477</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9013901948928833</v>
+        <v>0.900970458984375</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9311903715133667</v>
+        <v>0.9309202432632446</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03212849016620213</v>
       </c>
       <c r="C4" t="n">
-        <v>180</v>
+        <v>65</v>
       </c>
       <c r="D4" t="n">
-        <v>7566020</v>
+        <v>1359451</v>
       </c>
       <c r="E4" t="n">
-        <v>23473455</v>
+        <v>1695235</v>
       </c>
       <c r="F4" t="n">
-        <v>1621752</v>
+        <v>222526</v>
       </c>
       <c r="G4" t="n">
-        <v>93251</v>
+        <v>16049</v>
       </c>
       <c r="H4" t="n">
-        <v>183062</v>
+        <v>32027</v>
       </c>
       <c r="I4" t="n">
-        <v>15600</v>
+        <v>3032</v>
       </c>
       <c r="J4" t="n">
-        <v>2961</v>
+        <v>805</v>
       </c>
       <c r="K4" t="n">
-        <v>8160752</v>
+        <v>1506763</v>
       </c>
       <c r="L4" t="n">
-        <v>9041834</v>
+        <v>1377548</v>
       </c>
       <c r="M4" t="n">
-        <v>2971425</v>
+        <v>473053</v>
       </c>
       <c r="N4" t="n">
-        <v>657340</v>
+        <v>105843</v>
       </c>
       <c r="O4" t="n">
-        <v>1441868</v>
+        <v>208751</v>
       </c>
       <c r="P4" t="n">
-        <v>295581</v>
+        <v>34310</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999766945838928</v>
+        <v>0.999936580657959</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8598642945289612</v>
+        <v>0.7707131505012512</v>
       </c>
       <c r="S4" t="n">
-        <v>0.717090368270874</v>
+        <v>0.5296642184257507</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6240949630737305</v>
+        <v>0.3875179886817932</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2953763604164124</v>
+        <v>0.05432984605431557</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6735928058624268</v>
+        <v>0.4013092219829559</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7232329845428467</v>
+        <v>0.4131130278110504</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2072431</v>
+        <v>211003</v>
       </c>
       <c r="Z4" t="n">
-        <v>29981680</v>
+        <v>3027015</v>
       </c>
       <c r="AA4" t="n">
-        <v>831668</v>
+        <v>83549</v>
       </c>
       <c r="AB4" t="n">
-        <v>55444</v>
+        <v>5619</v>
       </c>
       <c r="AC4" t="n">
-        <v>11417</v>
+        <v>1131</v>
       </c>
       <c r="AD4" t="n">
-        <v>680</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2219228</v>
+        <v>225793</v>
       </c>
       <c r="AG4" t="n">
-        <v>2909869</v>
+        <v>291779</v>
       </c>
       <c r="AH4" t="n">
-        <v>1328156</v>
+        <v>133576</v>
       </c>
       <c r="AI4" t="n">
-        <v>302625</v>
+        <v>30510</v>
       </c>
       <c r="AJ4" t="n">
-        <v>499817</v>
+        <v>50160</v>
       </c>
       <c r="AK4" t="n">
-        <v>132578</v>
+        <v>13269</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9567984938621521</v>
+        <v>0.9561448693275452</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106762409210205</v>
+        <v>0.9107667803764343</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8575728535652161</v>
+        <v>0.8571337461471558</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6613578200340271</v>
+        <v>0.6601651310920715</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9016773700714111</v>
+        <v>0.9014432430267334</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.93132084608078</v>
+        <v>0.9312061071395874</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>489</v>
+        <v>192</v>
       </c>
       <c r="D5" t="n">
-        <v>424186</v>
+        <v>109794</v>
       </c>
       <c r="E5" t="n">
-        <v>2443382</v>
+        <v>379066</v>
       </c>
       <c r="F5" t="n">
-        <v>5595878</v>
+        <v>340197</v>
       </c>
       <c r="G5" t="n">
-        <v>208393</v>
+        <v>27455</v>
       </c>
       <c r="H5" t="n">
-        <v>631588</v>
+        <v>76016</v>
       </c>
       <c r="I5" t="n">
-        <v>61559</v>
+        <v>9804</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>6246091</v>
+        <v>921638</v>
       </c>
       <c r="L5" t="n">
-        <v>9479865</v>
+        <v>1633150</v>
       </c>
       <c r="M5" t="n">
-        <v>3769597</v>
+        <v>602327</v>
       </c>
       <c r="N5" t="n">
-        <v>626299</v>
+        <v>84510</v>
       </c>
       <c r="O5" t="n">
-        <v>1778604</v>
+        <v>331028</v>
       </c>
       <c r="P5" t="n">
-        <v>671305</v>
+        <v>134420</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999819397926331</v>
+        <v>0.9999509453773499</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9122390151023865</v>
+        <v>0.8520711064338684</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8871728777885437</v>
+        <v>0.8165997862815857</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9589362740516663</v>
+        <v>0.9344919323921204</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9921805858612061</v>
+        <v>0.988404393196106</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9803821444511414</v>
+        <v>0.9671187400817871</v>
       </c>
       <c r="W5" t="n">
-        <v>0.994110107421875</v>
+        <v>0.9897215962409973</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>80954</v>
+        <v>8141</v>
       </c>
       <c r="Z5" t="n">
-        <v>859027</v>
+        <v>87332</v>
       </c>
       <c r="AA5" t="n">
-        <v>8027267</v>
+        <v>807060</v>
       </c>
       <c r="AB5" t="n">
-        <v>99883</v>
+        <v>10049</v>
       </c>
       <c r="AC5" t="n">
-        <v>292014</v>
+        <v>29309</v>
       </c>
       <c r="AD5" t="n">
-        <v>6330</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2142751</v>
+        <v>213557</v>
       </c>
       <c r="AG5" t="n">
-        <v>2971640</v>
+        <v>301370</v>
       </c>
       <c r="AH5" t="n">
-        <v>1338208</v>
+        <v>135464</v>
       </c>
       <c r="AI5" t="n">
-        <v>303488</v>
+        <v>30611</v>
       </c>
       <c r="AJ5" t="n">
-        <v>503066</v>
+        <v>50697</v>
       </c>
       <c r="AK5" t="n">
-        <v>133120</v>
+        <v>13388</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.97342848777771</v>
+        <v>0.9732365012168884</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9641720652580261</v>
+        <v>0.9638676047325134</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837575554847717</v>
+        <v>0.9836111068725586</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963077902793884</v>
+        <v>0.9962767362594604</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938908219337463</v>
+        <v>0.9938561916351318</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.998381495475769</v>
+        <v>0.9983761310577393</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>571</v>
+        <v>127</v>
       </c>
       <c r="D6" t="n">
-        <v>135219</v>
+        <v>22411</v>
       </c>
       <c r="E6" t="n">
-        <v>180078</v>
+        <v>25859</v>
       </c>
       <c r="F6" t="n">
-        <v>211260</v>
+        <v>26728</v>
       </c>
       <c r="G6" t="n">
-        <v>269049</v>
+        <v>5468</v>
       </c>
       <c r="H6" t="n">
-        <v>89507</v>
+        <v>8326</v>
       </c>
       <c r="I6" t="n">
-        <v>9664</v>
+        <v>1059</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>65324</v>
+        <v>6613</v>
       </c>
       <c r="Z6" t="n">
-        <v>53793</v>
+        <v>5390</v>
       </c>
       <c r="AA6" t="n">
-        <v>109579</v>
+        <v>11097</v>
       </c>
       <c r="AB6" t="n">
-        <v>591860</v>
+        <v>59367</v>
       </c>
       <c r="AC6" t="n">
-        <v>69982</v>
+        <v>7030</v>
       </c>
       <c r="AD6" t="n">
-        <v>4810</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>727</v>
+        <v>224</v>
       </c>
       <c r="D7" t="n">
-        <v>33783</v>
+        <v>14210</v>
       </c>
       <c r="E7" t="n">
-        <v>345110</v>
+        <v>86231</v>
       </c>
       <c r="F7" t="n">
-        <v>887856</v>
+        <v>161039</v>
       </c>
       <c r="G7" t="n">
-        <v>303207</v>
+        <v>49071</v>
       </c>
       <c r="H7" t="n">
-        <v>3322977</v>
+        <v>180910</v>
       </c>
       <c r="I7" t="n">
-        <v>207921</v>
+        <v>20253</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>239</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>8106</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>298070</v>
+        <v>30121</v>
       </c>
       <c r="AB7" t="n">
-        <v>76193</v>
+        <v>7701</v>
       </c>
       <c r="AC7" t="n">
-        <v>4598515</v>
+        <v>461241</v>
       </c>
       <c r="AD7" t="n">
-        <v>120458</v>
+        <v>12057</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>582</v>
+        <v>41</v>
       </c>
       <c r="D8" t="n">
-        <v>1544</v>
+        <v>897</v>
       </c>
       <c r="E8" t="n">
-        <v>32529</v>
+        <v>10102</v>
       </c>
       <c r="F8" t="n">
-        <v>74793</v>
+        <v>23347</v>
       </c>
       <c r="G8" t="n">
-        <v>37051</v>
+        <v>10764</v>
       </c>
       <c r="H8" t="n">
-        <v>524806</v>
+        <v>89269</v>
       </c>
       <c r="I8" t="n">
-        <v>1263308</v>
+        <v>59385</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>280</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>810</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>3314</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>2660</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>126056</v>
+        <v>12679</v>
       </c>
       <c r="AD8" t="n">
-        <v>1801493</v>
+        <v>180417</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
